--- a/data/trans_orig/P16A20_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>400784</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402756</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>309584</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311545</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712330</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>714301</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1176276</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1178261</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>851838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>853785</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2030075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2032045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>364629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>366646</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232348</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>599005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>601037</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1945671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1947662</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1397753</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1399722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3345402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3347384</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>272339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>274341</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197220</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>471629</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>473686</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1132052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1134057</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>667585</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>669619</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1801659</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1803676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>186624</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>188705</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>471112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473172</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1690853</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1692866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1055605</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1057669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2748502</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2750535</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236791</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238757</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151512</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153501</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>390276</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>392258</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1157111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1159142</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>839623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>841563</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1998712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2000705</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>299131</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246824</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546015</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1697069</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1699101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1239940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1241888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2938993</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2940990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023</t>
+          <t>Población según si ha consumido medicamentos para la alteración del tiroides en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7092</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18852</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66646</t>
+          <t>66186</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>99206</t>
+          <t>98071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76516</t>
+          <t>77780</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>113108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>495090</t>
+          <t>494693</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506850</t>
+          <t>506976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652856</t>
+          <t>653991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>685416</t>
+          <t>685876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1153582</t>
+          <t>1152896</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1189488</t>
+          <t>1188224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,86%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41857</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160645</t>
+          <t>159943</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>914664</t>
+          <t>808594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174704</t>
+          <t>175843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1111147</t>
+          <t>1041461</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2248470</t>
+          <t>2249257</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2275678</t>
+          <t>2275265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1322123</t>
+          <t>1428193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2076142</t>
+          <t>2076844</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3415967</t>
+          <t>3485653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4352410</t>
+          <t>4351271</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13764</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37355</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61233</t>
+          <t>59507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44560</t>
+          <t>44134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70075</t>
+          <t>68769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632859</t>
+          <t>631671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642751</t>
+          <t>642861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>598583</t>
+          <t>600309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>622461</t>
+          <t>623040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1236364</t>
+          <t>1237670</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1261879</t>
+          <t>1262305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31461</t>
+          <t>31194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62875</t>
+          <t>62374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287110</t>
+          <t>285759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1089467</t>
+          <t>1089978</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320677</t>
+          <t>323290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105238</t>
+          <t>1307597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3388017</t>
+          <t>3388518</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3419431</t>
+          <t>3419698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2559198</t>
+          <t>2558687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3361555</t>
+          <t>3362906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5994319</t>
+          <t>5791960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6778880</t>
+          <t>6776267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A20_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A20_2023-Estudios-trans_orig.xlsx
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>78912</t>
+          <t>80623</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66186</t>
+          <t>69061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98071</t>
+          <t>95346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>90583</t>
+          <t>93078</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77780</t>
+          <t>79768</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>108449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>502271</t>
+          <t>565087</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>494693</t>
+          <t>557555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>506976</t>
+          <t>570507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>673150</t>
+          <t>739493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653991</t>
+          <t>724770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>685876</t>
+          <t>751055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1175421</t>
+          <t>1304580</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1152896</t>
+          <t>1289209</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1188224</t>
+          <t>1317890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>752062</t>
+          <t>820116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1266004</t>
+          <t>1397658</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,27 +5880,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25769</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>39974</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>358036</t>
+          <t>175889</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>159943</t>
+          <t>156412</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>808594</t>
+          <t>201269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>383804</t>
+          <t>201433</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>175843</t>
+          <t>178656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1041461</t>
+          <t>227092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -5993,22 +5993,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2264558</t>
+          <t>2205021</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2249257</t>
+          <t>2190592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2275265</t>
+          <t>2214285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1878751</t>
+          <t>1994440</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1428193</t>
+          <t>1969060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2076844</t>
+          <t>2013917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4143310</t>
+          <t>4199462</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3485653</t>
+          <t>4173803</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4351271</t>
+          <t>4222239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236787</t>
+          <t>2170329</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236787</t>
+          <t>2170329</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236787</t>
+          <t>2170329</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527114</t>
+          <t>4400895</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527114</t>
+          <t>4400895</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527114</t>
+          <t>4400895</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48079</t>
+          <t>53156</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>42551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>66844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55764</t>
+          <t>62559</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44134</t>
+          <t>51253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68769</t>
+          <t>76891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>638938</t>
+          <t>702183</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631671</t>
+          <t>693982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642861</t>
+          <t>706625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>611737</t>
+          <t>680997</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>600309</t>
+          <t>667309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>623040</t>
+          <t>691602</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1250675</t>
+          <t>1383181</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1237670</t>
+          <t>1368849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1262305</t>
+          <t>1394487</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659816</t>
+          <t>734153</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659816</t>
+          <t>734153</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659816</t>
+          <t>734153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306439</t>
+          <t>1445740</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306439</t>
+          <t>1445740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306439</t>
+          <t>1445740</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31194</t>
+          <t>35230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62374</t>
+          <t>62746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>485027</t>
+          <t>309667</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>285759</t>
+          <t>283859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1089978</t>
+          <t>341149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>530151</t>
+          <t>357071</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323290</t>
+          <t>329018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1307597</t>
+          <t>390864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3405768</t>
+          <t>3472291</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3388518</t>
+          <t>3456949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3419698</t>
+          <t>3484465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3163638</t>
+          <t>3414931</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2558687</t>
+          <t>3383449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3362906</t>
+          <t>3440739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6569406</t>
+          <t>6887222</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5791960</t>
+          <t>6853429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6776267</t>
+          <t>6915275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3648665</t>
+          <t>3724598</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3648665</t>
+          <t>3724598</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3648665</t>
+          <t>3724598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099557</t>
+          <t>7244293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099557</t>
+          <t>7244293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099557</t>
+          <t>7244293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
